--- a/public/templates/examples/A-091-ThreatIntelligenceRoutingDistributionMatrix-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-091-ThreatIntelligenceRoutingDistributionMatrix-EXAMPLE-M.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="6">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -198,12 +198,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="552450" cy="552450"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -342,7 +342,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -376,7 +376,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/examples/A-091-ThreatIntelligenceRoutingDistributionMatrix-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-091-ThreatIntelligenceRoutingDistributionMatrix-EXAMPLE-M.xlsx
@@ -4,19 +4,21 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Aptos"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -116,6 +118,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -586,7 +591,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -748,7 +753,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="19.5" customHeight="1">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>MS-ISAC advisories</t>
@@ -770,7 +775,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="19.5" customHeight="1">
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>CISA alerts &amp; advisories</t>
@@ -792,7 +797,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="19.5" customHeight="1">
+    <row r="19" ht="34.7" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Indiana IOT / IN-ISAC bulletins</t>
@@ -814,7 +819,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="19.5" customHeight="1">
+    <row r="20" ht="34.7" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>CAD vendor security advisories</t>
@@ -836,7 +841,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="19.5" customHeight="1">
+    <row r="21" ht="34.7" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>ESInet provider notices</t>
@@ -858,7 +863,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="19.5" customHeight="1">
+    <row r="22" ht="34.7" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Regional public-safety peer group</t>
@@ -930,7 +935,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="19.5" customHeight="1">
+    <row r="26" ht="34.7" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>MS-ISAC advisories</t>
@@ -972,7 +977,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="19.5" customHeight="1">
+    <row r="27" ht="34.7" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>CISA alerts &amp; advisories</t>
@@ -1014,7 +1019,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="19.5" customHeight="1">
+    <row r="28" ht="34.7" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Indiana IOT / IN-ISAC bulletins</t>
@@ -1056,7 +1061,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="19.5" customHeight="1">
+    <row r="29" ht="34.7" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>CAD vendor security advisories</t>
@@ -1098,7 +1103,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="19.5" customHeight="1">
+    <row r="30" ht="34.7" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>ESInet provider notices</t>
@@ -1140,7 +1145,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="19.5" customHeight="1">
+    <row r="31" ht="34.7" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Regional public-safety peer group</t>
@@ -1270,10 +1275,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="B45" s="10">
+        <v>46057</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -1313,7 +1316,8 @@
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>